--- a/src/test/resources/recruitmentsourcing.xlsx
+++ b/src/test/resources/recruitmentsourcing.xlsx
@@ -428,7 +428,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0.5</v>
